--- a/src/test/resources/TestData/OCW_TestCases.xlsx
+++ b/src/test/resources/TestData/OCW_TestCases.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varti\eclipse-workspace\CucumberJava\src\test\resources\TestData\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0E797BF-C41D-41F7-8ADB-626033234254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2810" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="6800"/>
   </bookViews>
   <sheets>
     <sheet name="OCWTestData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="32">
   <si>
     <t>Scenario</t>
   </si>
@@ -42,6 +44,42 @@
     <t>Password</t>
   </si>
   <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>MeterStatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Previous Meter Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+current Meter Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+system Reading</t>
+  </si>
+  <si>
+    <t>current Water Charges</t>
+  </si>
+  <si>
+    <t>raw Water Surcharge</t>
+  </si>
+  <si>
+    <t>electricity Surcharge</t>
+  </si>
+  <si>
+    <t>meterRent</t>
+  </si>
+  <si>
+    <t>otherCharges</t>
+  </si>
+  <si>
+    <t>uploadImage</t>
+  </si>
+  <si>
     <t>User should be able to login with valid credentials</t>
   </si>
   <si>
@@ -51,52 +89,387 @@
     <t>TC_01LoginFuctionality</t>
   </si>
   <si>
+    <t>atul.gondane@veolia.com</t>
+  </si>
+  <si>
     <t>Test@123</t>
   </si>
   <si>
-    <t>anand.dhepe@veolia.com</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Verify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>user</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>able</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>navigate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>to</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>bill</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Generation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>page</t>
+    </r>
+  </si>
+  <si>
+    <t>TC02</t>
+  </si>
+  <si>
+    <t>TC_02BillGeneration_001</t>
+  </si>
+  <si>
+    <t>53001432</t>
+  </si>
+  <si>
+    <t>Meter Ok</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>C:\Users\varti\Pictures\Screenshots\Screenshot 2025-05-14 114823 - Copy.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0080FF"/>
       <name val="Consolas"/>
-      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,18 +478,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -126,26 +673,266 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -156,20 +943,71 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -218,7 +1056,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -253,7 +1091,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -427,66 +1265,2605 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" customWidth="1"/>
-    <col min="4" max="4" width="27.81640625" customWidth="1"/>
-    <col min="5" max="5" width="18.453125" customWidth="1"/>
+    <col min="1" max="1" width="24.6363636363636" customWidth="1"/>
+    <col min="2" max="2" width="13.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="25.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="24.2727272727273" customWidth="1"/>
+    <col min="5" max="5" width="18.4545454545455" customWidth="1"/>
+    <col min="6" max="6" width="13.1818181818182" customWidth="1"/>
+    <col min="7" max="7" width="16.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="28.3636363636364" customWidth="1"/>
+    <col min="9" max="9" width="24.1818181818182" customWidth="1"/>
+    <col min="10" max="10" width="18.9090909090909" customWidth="1"/>
+    <col min="11" max="11" width="23.9090909090909" customWidth="1"/>
+    <col min="12" max="12" width="22.3636363636364" customWidth="1"/>
+    <col min="13" max="13" width="20.8181818181818" customWidth="1"/>
+    <col min="14" max="14" width="13.6363636363636" customWidth="1"/>
+    <col min="15" max="15" width="14.5454545454545" customWidth="1"/>
+    <col min="16" max="16" width="14.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:16">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" ht="39" spans="1:16">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="39" spans="1:16">
+      <c r="A3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="39" spans="1:16">
+      <c r="A4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="9">
+        <v>12000601</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="39" spans="1:16">
+      <c r="A5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="9">
+        <v>12000946</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" ht="39" spans="1:16">
+      <c r="A6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="9">
+        <v>13000193</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="39" spans="1:16">
+      <c r="A7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="9">
+        <v>14000889</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" ht="39" spans="1:16">
+      <c r="A8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="9">
+        <v>14001057</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" ht="39" spans="1:16">
+      <c r="A9" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="9">
+        <v>16002276</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" ht="39" spans="1:16">
+      <c r="A10" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="9">
+        <v>16002402</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="39" spans="1:16">
+      <c r="A11" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="9">
+        <v>16002407</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" ht="39" spans="1:16">
+      <c r="A12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="9">
+        <v>16002408</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P12" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" ht="39" spans="1:16">
+      <c r="A13" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="9">
+        <v>16004966</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" ht="39" spans="1:16">
+      <c r="A14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9">
+        <v>16006676</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" ht="39" spans="1:16">
+      <c r="A15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="9">
+        <v>16006780</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" ht="39" spans="1:16">
+      <c r="A16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="9">
+        <v>16014600</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" ht="39" spans="1:16">
+      <c r="A17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="9">
+        <v>16018509</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P17" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" ht="39" spans="1:16">
+      <c r="A18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="9">
+        <v>16018692</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O18" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P18" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" ht="39" spans="1:16">
+      <c r="A19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="9">
+        <v>16019699</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" ht="39" spans="1:16">
+      <c r="A20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="9">
+        <v>16019707</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O20" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" ht="39" spans="1:16">
+      <c r="A21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="9">
+        <v>16024878</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P21" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" ht="39" spans="1:16">
+      <c r="A22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="9">
+        <v>16026714</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" ht="39" spans="1:16">
+      <c r="A23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="9">
+        <v>16026715</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O23" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P23" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" ht="39" spans="1:16">
+      <c r="A24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="9">
+        <v>16027832</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O24" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P24" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" ht="39" spans="1:16">
+      <c r="A25" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="9">
+        <v>16027863</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P25" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" ht="39" spans="1:16">
+      <c r="A26" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="9">
+        <v>16028954</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P26" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" ht="39" spans="1:16">
+      <c r="A27" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="9">
+        <v>16034138</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" ht="39" spans="1:16">
+      <c r="A28" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="9">
+        <v>16034992</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" ht="39" spans="1:16">
+      <c r="A29" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="9">
+        <v>16039395</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" ht="39" spans="1:16">
+      <c r="A30" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="9">
+        <v>16040144</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P30" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" ht="39" spans="1:16">
+      <c r="A31" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="9">
+        <v>16040377</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O31" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P31" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" ht="39" spans="1:16">
+      <c r="A32" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="9">
+        <v>16041848</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N32" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O32" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" ht="39" spans="1:16">
+      <c r="A33" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="9">
+        <v>16041885</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O33" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P33" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" ht="39" spans="1:16">
+      <c r="A34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="9">
+        <v>16043938</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N34" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O34" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P34" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" ht="39" spans="1:16">
+      <c r="A35" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="9">
+        <v>16045139</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P35" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" ht="39" spans="1:16">
+      <c r="A36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="9">
+        <v>16046050</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O36" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P36" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" ht="39" spans="1:16">
+      <c r="A37" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="9">
+        <v>16049704</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O37" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P37" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" ht="39" spans="1:16">
+      <c r="A38" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="9">
+        <v>16051864</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O38" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P38" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" ht="39" spans="1:16">
+      <c r="A39" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="9">
+        <v>16052214</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" ht="39" spans="1:16">
+      <c r="A40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="9">
+        <v>16052439</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N40" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O40" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P40" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" ht="39" spans="1:16">
+      <c r="A41" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="9">
+        <v>16052808</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N41" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O41" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P41" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" ht="39" spans="1:16">
+      <c r="A42" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F42" s="9">
+        <v>16055202</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N42" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O42" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P42" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" ht="39" spans="1:16">
+      <c r="A43" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F43" s="9">
+        <v>16055840</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N43" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O43" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" ht="39" spans="1:16">
+      <c r="A44" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F44" s="9">
+        <v>16058268</v>
+      </c>
+      <c r="G44" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N44" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O44" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P44" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="45" ht="39" spans="1:16">
+      <c r="A45" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F45" s="9">
+        <v>16059624</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P45" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="46" ht="39" spans="1:16">
+      <c r="A46" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F46" s="9">
+        <v>16059893</v>
+      </c>
+      <c r="G46" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O46" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P46" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" ht="39" spans="1:16">
+      <c r="A47" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F47" s="9">
+        <v>16059925</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N47" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O47" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P47" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" ht="39" spans="1:16">
+      <c r="A48" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F48" s="9">
+        <v>16060126</v>
+      </c>
+      <c r="G48" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O48" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P48" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" ht="39" spans="1:16">
+      <c r="A49" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="9">
+        <v>16060777</v>
+      </c>
+      <c r="G49" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O49" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P49" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" ht="39" spans="1:16">
+      <c r="A50" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" s="9">
+        <v>16060911</v>
+      </c>
+      <c r="G50" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N50" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O50" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="P50" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{548551CB-FCBF-4B34-8A93-A5C4C938C7AF}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{FDD1E3DE-E91B-48F0-9281-C03854865A3C}"/>
+    <hyperlink ref="D2" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="E2" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="D3" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="E3" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="D4" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D5" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D6" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D7" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D8" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D9" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D10" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D11" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D12" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D13" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D14" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D15" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D16" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D17" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D18" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D19" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D20" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D21" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D22" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D23" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D24" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D25" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D26" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D27" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D28" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D29" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D30" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D31" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D32" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D33" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D34" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D35" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D36" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D37" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D38" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D39" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D40" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D41" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D42" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D43" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D44" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D45" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D46" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D47" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D48" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D49" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="D50" r:id="rId1" display="atul.gondane@veolia.com" tooltip="mailto:atul.gondane@veolia.com"/>
+    <hyperlink ref="E4" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E5" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E6" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E7" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E8" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E9" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E10" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E11" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E12" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E13" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E14" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E15" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E16" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E17" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E18" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E19" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E20" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E21" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E22" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E23" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E24" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E25" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E26" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E27" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E28" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E29" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E30" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E31" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E32" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E33" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E34" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E35" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E36" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E37" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E38" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E39" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E40" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E41" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E42" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E43" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E44" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E45" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E46" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E47" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E48" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E49" r:id="rId2" display="Test@123"/>
+    <hyperlink ref="E50" r:id="rId2" display="Test@123"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>